--- a/database/event/3491/event_3491_evp_summary.xlsx
+++ b/database/event/3491/event_3491_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.099600000000001</v>
+        <v>9.749000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>5.3995</v>
+        <v>5.7849</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2547</v>
+        <v>3.4401</v>
       </c>
       <c r="E2" t="n">
-        <v>9.099600000000001</v>
+        <v>9.749000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6084</v>
+        <v>3.2578</v>
       </c>
       <c r="G2" t="n">
         <v>6.4912</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6084</v>
+        <v>3.2578</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6084</v>
+        <v>3.2578</v>
       </c>
       <c r="J2" t="n">
         <v>6.5604</v>
@@ -529,7 +529,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>9.168799999999999</v>
+        <v>9.818199999999999</v>
       </c>
       <c r="N2" t="n">
         <v>258</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8337</v>
+        <v>7.9874</v>
       </c>
       <c r="C3" t="n">
-        <v>4.6484</v>
+        <v>4.7396</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7433</v>
+        <v>2.7383</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8337</v>
+        <v>7.9874</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1234</v>
+        <v>2.2772</v>
       </c>
       <c r="G3" t="n">
         <v>5.7102</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1234</v>
+        <v>2.2772</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1234</v>
+        <v>2.2772</v>
       </c>
       <c r="J3" t="n">
         <v>5.7102</v>
@@ -575,7 +575,7 @@
         <v>145</v>
       </c>
       <c r="M3" t="n">
-        <v>7.833600000000001</v>
+        <v>7.987400000000001</v>
       </c>
       <c r="N3" t="n">
         <v>231</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9666</v>
+        <v>7.6687</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1338</v>
+        <v>4.5505</v>
       </c>
       <c r="D4" t="n">
-        <v>2.393</v>
+        <v>2.6113</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9666</v>
+        <v>7.6687</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6035</v>
+        <v>3.3056</v>
       </c>
       <c r="G4" t="n">
         <v>4.3631</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6035</v>
+        <v>3.3056</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6035</v>
+        <v>3.3056</v>
       </c>
       <c r="J4" t="n">
         <v>4.3631</v>
@@ -621,7 +621,7 @@
         <v>145</v>
       </c>
       <c r="M4" t="n">
-        <v>6.9666</v>
+        <v>7.6687</v>
       </c>
       <c r="N4" t="n">
         <v>231</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7041</v>
+        <v>7.5984</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9781</v>
+        <v>4.5087</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2869</v>
+        <v>2.5833</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7041</v>
+        <v>7.5984</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3325</v>
+        <v>3.2268</v>
       </c>
       <c r="G5" t="n">
         <v>4.3715</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3325</v>
+        <v>3.2268</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3325</v>
+        <v>3.2268</v>
       </c>
       <c r="J5" t="n">
         <v>4.3715</v>
@@ -667,7 +667,7 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>6.704000000000001</v>
+        <v>7.5983</v>
       </c>
       <c r="N5" t="n">
         <v>258</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.037</v>
+        <v>6.3092</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5822</v>
+        <v>3.7438</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0175</v>
+        <v>2.0697</v>
       </c>
       <c r="E6" t="n">
-        <v>6.037</v>
+        <v>6.3092</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6244</v>
+        <v>3.4929</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4126</v>
+        <v>2.8163</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6244</v>
+        <v>3.4929</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6244</v>
+        <v>3.4929</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4126</v>
+        <v>2.8163</v>
       </c>
       <c r="K6" t="n">
         <v>86</v>
@@ -713,7 +713,7 @@
         <v>145</v>
       </c>
       <c r="M6" t="n">
-        <v>6.037000000000001</v>
+        <v>6.309200000000001</v>
       </c>
       <c r="N6" t="n">
         <v>231</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.4191</v>
+        <v>6.037</v>
       </c>
       <c r="C7" t="n">
-        <v>3.2156</v>
+        <v>3.5822</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7678</v>
+        <v>1.9612</v>
       </c>
       <c r="E7" t="n">
-        <v>5.4191</v>
+        <v>6.037</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6028</v>
+        <v>1.6244</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8163</v>
+        <v>4.4126</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6028</v>
+        <v>1.6244</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6028</v>
+        <v>1.6244</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8163</v>
+        <v>4.4126</v>
       </c>
       <c r="K7" t="n">
         <v>86</v>
@@ -759,7 +759,7 @@
         <v>145</v>
       </c>
       <c r="M7" t="n">
-        <v>5.4191</v>
+        <v>6.037000000000001</v>
       </c>
       <c r="N7" t="n">
         <v>231</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6528</v>
+        <v>5.4162</v>
       </c>
       <c r="C8" t="n">
-        <v>2.7609</v>
+        <v>3.2139</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4583</v>
+        <v>1.7139</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6528</v>
+        <v>5.4162</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1662</v>
+        <v>3.9296</v>
       </c>
       <c r="G8" t="n">
         <v>1.4866</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1662</v>
+        <v>3.9296</v>
       </c>
       <c r="I8" t="n">
-        <v>3.181</v>
+        <v>3.9627</v>
       </c>
       <c r="J8" t="n">
         <v>1.4866</v>
@@ -805,7 +805,7 @@
         <v>124</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6676</v>
+        <v>5.4493</v>
       </c>
       <c r="N8" t="n">
         <v>277</v>
@@ -814,173 +814,173 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9066</v>
+        <v>3.4432</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7247</v>
+        <v>2.0431</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7528</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9066</v>
+        <v>3.4432</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5454</v>
+        <v>4.4432</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6388</v>
+        <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5454</v>
+        <v>4.6639</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5619</v>
+        <v>4.6639</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6388</v>
+        <v>-1</v>
       </c>
       <c r="K9" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9231</v>
+        <v>3.6639</v>
       </c>
       <c r="N9" t="n">
-        <v>215</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8755</v>
+        <v>3.2784</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7063</v>
+        <v>1.9453</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7403</v>
+        <v>0.8622</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8755</v>
+        <v>3.2784</v>
       </c>
       <c r="F10" t="n">
-        <v>2.968</v>
+        <v>3.9172</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0925</v>
+        <v>-0.6388</v>
       </c>
       <c r="H10" t="n">
-        <v>2.968</v>
+        <v>3.9172</v>
       </c>
       <c r="I10" t="n">
-        <v>2.968</v>
+        <v>3.9502</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0925</v>
+        <v>-0.6388</v>
       </c>
       <c r="K10" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="L10" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8755</v>
+        <v>3.3114</v>
       </c>
       <c r="N10" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7825</v>
+        <v>3.1092</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6511</v>
+        <v>1.8449</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7027</v>
+        <v>0.7948</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7825</v>
+        <v>3.1092</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6758</v>
+        <v>2.7608</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1067</v>
+        <v>0.3484</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6758</v>
+        <v>2.7608</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6758</v>
+        <v>2.7608</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1067</v>
+        <v>0.3484</v>
       </c>
       <c r="K11" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="L11" t="n">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7825</v>
+        <v>3.1092</v>
       </c>
       <c r="N11" t="n">
-        <v>242</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7461</v>
+        <v>2.8755</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6295</v>
+        <v>1.7063</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7017</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7461</v>
+        <v>2.8755</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7461</v>
+        <v>2.968</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>-0.0925</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7461</v>
+        <v>2.968</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7461</v>
+        <v>2.968</v>
       </c>
       <c r="J12" t="n">
-        <v>-1</v>
+        <v>-0.0925</v>
       </c>
       <c r="K12" t="n">
         <v>125</v>
@@ -989,7 +989,7 @@
         <v>49</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7461</v>
+        <v>2.8755</v>
       </c>
       <c r="N12" t="n">
         <v>174</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5836</v>
+        <v>2.8648</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5331</v>
+        <v>1.6999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6224</v>
+        <v>0.6974</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5836</v>
+        <v>2.8648</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2352</v>
+        <v>2.2438</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3484</v>
+        <v>0.621</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2352</v>
+        <v>2.2438</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2352</v>
+        <v>2.2438</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3484</v>
+        <v>0.621</v>
       </c>
       <c r="K13" t="n">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="L13" t="n">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5836</v>
+        <v>2.8648</v>
       </c>
       <c r="N13" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5687</v>
+        <v>2.7825</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5242</v>
+        <v>1.6511</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6163</v>
+        <v>0.6646</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5687</v>
+        <v>2.7825</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2677</v>
+        <v>1.6758</v>
       </c>
       <c r="G14" t="n">
-        <v>0.301</v>
+        <v>1.1067</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2677</v>
+        <v>1.6758</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2783</v>
+        <v>1.6758</v>
       </c>
       <c r="J14" t="n">
-        <v>0.301</v>
+        <v>1.1067</v>
       </c>
       <c r="K14" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5793</v>
+        <v>2.7825</v>
       </c>
       <c r="N14" t="n">
-        <v>215</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5192</v>
+        <v>2.6812</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4948</v>
+        <v>1.591</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.6243</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5192</v>
+        <v>2.6812</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9482</v>
+        <v>2.1102</v>
       </c>
       <c r="G15" t="n">
         <v>0.571</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9482</v>
+        <v>2.1102</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9573</v>
+        <v>2.128</v>
       </c>
       <c r="J15" t="n">
         <v>0.571</v>
@@ -1127,7 +1127,7 @@
         <v>124</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5283</v>
+        <v>2.699</v>
       </c>
       <c r="N15" t="n">
         <v>277</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2182</v>
+        <v>2.5602</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3162</v>
+        <v>1.5192</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4747</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2182</v>
+        <v>2.5602</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5972</v>
+        <v>2.2592</v>
       </c>
       <c r="G16" t="n">
-        <v>0.621</v>
+        <v>0.301</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5972</v>
+        <v>2.2592</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5972</v>
+        <v>2.2783</v>
       </c>
       <c r="J16" t="n">
-        <v>0.621</v>
+        <v>0.301</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="L16" t="n">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2182</v>
+        <v>2.5793</v>
       </c>
       <c r="N16" t="n">
-        <v>242</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8094</v>
+        <v>2.3074</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0737</v>
+        <v>1.3692</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3096</v>
+        <v>0.4754</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8094</v>
+        <v>2.3074</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3454</v>
+        <v>1.8434</v>
       </c>
       <c r="G17" t="n">
         <v>0.464</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3454</v>
+        <v>1.8434</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3517</v>
+        <v>1.8589</v>
       </c>
       <c r="J17" t="n">
         <v>0.464</v>
@@ -1219,7 +1219,7 @@
         <v>124</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8157</v>
+        <v>2.3229</v>
       </c>
       <c r="N17" t="n">
         <v>277</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6613</v>
+        <v>1.7772</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9858</v>
+        <v>1.0546</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2498</v>
+        <v>0.2641</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6613</v>
+        <v>1.7772</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6808</v>
+        <v>1.0573</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0195</v>
+        <v>0.7199</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6808</v>
+        <v>1.0573</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6808</v>
+        <v>1.0573</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0195</v>
+        <v>0.7199</v>
       </c>
       <c r="K18" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6613</v>
+        <v>1.7772</v>
       </c>
       <c r="N18" t="n">
-        <v>182</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6377</v>
+        <v>1.6631</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9718</v>
+        <v>0.9869</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2402</v>
+        <v>0.2187</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6377</v>
+        <v>1.6631</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9177999999999999</v>
+        <v>1.6826</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7199</v>
+        <v>-0.0195</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9177999999999999</v>
+        <v>1.6826</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9177999999999999</v>
+        <v>1.6826</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7199</v>
+        <v>-0.0195</v>
       </c>
       <c r="K19" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L19" t="n">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6377</v>
+        <v>1.6631</v>
       </c>
       <c r="N19" t="n">
-        <v>242</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20">
@@ -1330,7 +1330,7 @@
         <v>0.8864</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1821</v>
+        <v>0.1512</v>
       </c>
       <c r="E20" t="n">
         <v>1.4938</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4303</v>
+        <v>1.4231</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8487</v>
+        <v>0.8444</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1564</v>
+        <v>0.1231</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4303</v>
+        <v>1.4231</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9342</v>
+        <v>1.927</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5039</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9342</v>
+        <v>1.927</v>
       </c>
       <c r="I21" t="n">
         <v>1.9432</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1865</v>
+        <v>1.2356</v>
       </c>
       <c r="C22" t="n">
-        <v>0.704</v>
+        <v>0.7332</v>
       </c>
       <c r="D22" t="n">
-        <v>0.058</v>
+        <v>0.0484</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1865</v>
+        <v>1.2356</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1865</v>
+        <v>1.2356</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1865</v>
+        <v>1.2356</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1865</v>
+        <v>1.2356</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1865</v>
+        <v>1.2356</v>
       </c>
       <c r="N22" t="n">
         <v>173</v>
@@ -1458,1182 +1458,1182 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.135</v>
+        <v>1.1931</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6735</v>
+        <v>0.708</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0372</v>
+        <v>0.0314</v>
       </c>
       <c r="E23" t="n">
-        <v>1.135</v>
+        <v>1.1931</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8106</v>
+        <v>1.1931</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3244</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8106</v>
+        <v>1.1931</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8106</v>
+        <v>1.1931</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3244</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L23" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.135</v>
+        <v>1.1931</v>
       </c>
       <c r="N23" t="n">
-        <v>182</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.105</v>
+        <v>1.1411</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6771</v>
       </c>
       <c r="D24" t="n">
-        <v>0.025</v>
+        <v>0.0107</v>
       </c>
       <c r="E24" t="n">
-        <v>1.105</v>
+        <v>1.1411</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6597</v>
+        <v>1.1411</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4453</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6597</v>
+        <v>1.1411</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6597</v>
+        <v>1.1411</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4453</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="L24" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.105</v>
+        <v>1.1411</v>
       </c>
       <c r="N24" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0811</v>
+        <v>1.135</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6415</v>
+        <v>0.6735</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0154</v>
+        <v>0.0083</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0811</v>
+        <v>1.135</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0811</v>
+        <v>0.8106</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.3244</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0811</v>
+        <v>0.8106</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0811</v>
+        <v>0.8106</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.3244</v>
       </c>
       <c r="K25" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0811</v>
+        <v>1.135</v>
       </c>
       <c r="N25" t="n">
-        <v>101</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.0739</v>
+        <v>1.105</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6372</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0125</v>
+        <v>-0.0037</v>
       </c>
       <c r="E26" t="n">
-        <v>1.0739</v>
+        <v>1.105</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7493</v>
+        <v>0.6597</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3246</v>
+        <v>0.4453</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7493</v>
+        <v>0.6597</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7493</v>
+        <v>0.6597</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3246</v>
+        <v>0.4453</v>
       </c>
       <c r="K26" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L26" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0739</v>
+        <v>1.105</v>
       </c>
       <c r="N26" t="n">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9852</v>
+        <v>1.0739</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5846</v>
+        <v>0.6372</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0234</v>
+        <v>-0.0161</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9852</v>
+        <v>1.0739</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9852</v>
+        <v>0.7493</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.3246</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9852</v>
+        <v>0.7493</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9852</v>
+        <v>0.7493</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.3246</v>
       </c>
       <c r="K27" t="n">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9852</v>
+        <v>1.0739</v>
       </c>
       <c r="N27" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8313</v>
+        <v>0.9066</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4933</v>
+        <v>0.538</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0827</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8313</v>
+        <v>0.9066</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0695</v>
+        <v>0.9066</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2382</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0695</v>
+        <v>0.9066</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0695</v>
+        <v>0.9066</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2382</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L28" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8312999999999999</v>
+        <v>0.9066</v>
       </c>
       <c r="N28" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8216</v>
+        <v>0.8908</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4875</v>
+        <v>0.5286</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0895</v>
+        <v>-0.089</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8216</v>
+        <v>0.8908</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8216</v>
+        <v>1.1709</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.2801</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8216</v>
+        <v>1.1709</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8216</v>
+        <v>1.1709</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.2801</v>
       </c>
       <c r="K29" t="n">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8216</v>
+        <v>0.8908</v>
       </c>
       <c r="N29" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7043</v>
+        <v>0.8313</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4179</v>
+        <v>0.4933</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1368</v>
+        <v>-0.1127</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7043</v>
+        <v>0.8313</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7212</v>
+        <v>1.0695</v>
       </c>
       <c r="G30" t="n">
-        <v>1.4255</v>
+        <v>-0.2382</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7212</v>
+        <v>1.0695</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7212</v>
+        <v>1.0695</v>
       </c>
       <c r="J30" t="n">
-        <v>1.4255</v>
+        <v>-0.2382</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L30" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7043</v>
+        <v>0.8312999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>258</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6812</v>
+        <v>0.8188</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4042</v>
+        <v>0.4859</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1462</v>
+        <v>-0.1177</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6812</v>
+        <v>0.8188</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4818</v>
+        <v>1.8066</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1994</v>
+        <v>-0.9878</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4818</v>
+        <v>1.8066</v>
       </c>
       <c r="I31" t="n">
-        <v>0.484</v>
+        <v>1.8066</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1994</v>
+        <v>-0.9878</v>
       </c>
       <c r="K31" t="n">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="L31" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6834</v>
+        <v>0.8188</v>
       </c>
       <c r="N31" t="n">
-        <v>215</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6667</v>
+        <v>0.7159</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3956</v>
+        <v>0.4248</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.152</v>
+        <v>-0.1587</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6667</v>
+        <v>0.7159</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8733</v>
+        <v>0.2937</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2066</v>
+        <v>0.4222</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8733</v>
+        <v>0.2937</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8733</v>
+        <v>0.2937</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2066</v>
+        <v>0.4222</v>
       </c>
       <c r="K32" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="L32" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6667</v>
+        <v>0.7159</v>
       </c>
       <c r="N32" t="n">
-        <v>258</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6288</v>
+        <v>0.7043</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3731</v>
+        <v>0.4179</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1673</v>
+        <v>-0.1633</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6288</v>
+        <v>0.7043</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6166</v>
+        <v>-0.7212</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.9878</v>
+        <v>1.4255</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6166</v>
+        <v>-0.7212</v>
       </c>
       <c r="I33" t="n">
-        <v>1.6166</v>
+        <v>-0.7212</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9878</v>
+        <v>1.4255</v>
       </c>
       <c r="K33" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6288</v>
+        <v>0.7043</v>
       </c>
       <c r="N33" t="n">
-        <v>164</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5333</v>
+        <v>0.6794</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3164</v>
+        <v>0.4031</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2059</v>
+        <v>-0.1732</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5333</v>
+        <v>0.6794</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5333</v>
+        <v>0.48</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.1994</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5333</v>
+        <v>0.48</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5333</v>
+        <v>0.484</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.1994</v>
       </c>
       <c r="K34" t="n">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5333</v>
+        <v>0.6834</v>
       </c>
       <c r="N34" t="n">
-        <v>97</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.482</v>
+        <v>0.6713</v>
       </c>
       <c r="C35" t="n">
-        <v>0.286</v>
+        <v>0.3983</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2266</v>
+        <v>-0.1765</v>
       </c>
       <c r="E35" t="n">
-        <v>0.482</v>
+        <v>0.6713</v>
       </c>
       <c r="F35" t="n">
-        <v>0.482</v>
+        <v>0.6713</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.482</v>
+        <v>0.6713</v>
       </c>
       <c r="I35" t="n">
-        <v>0.482</v>
+        <v>0.6713</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.482</v>
+        <v>0.6713</v>
       </c>
       <c r="N35" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4484</v>
+        <v>0.6667</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2661</v>
+        <v>0.3956</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2402</v>
+        <v>-0.1783</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4484</v>
+        <v>0.6667</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4484</v>
+        <v>0.8733</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.2066</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4484</v>
+        <v>0.8733</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4484</v>
+        <v>0.8733</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.2066</v>
       </c>
       <c r="K36" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4484</v>
+        <v>0.6667</v>
       </c>
       <c r="N36" t="n">
-        <v>48</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4337</v>
+        <v>0.6133</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2573</v>
+        <v>0.3639</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2462</v>
+        <v>-0.1996</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4337</v>
+        <v>0.6133</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4337</v>
+        <v>1.6108</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4337</v>
+        <v>1.6108</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4337</v>
+        <v>1.6108</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="K37" t="n">
+        <v>125</v>
+      </c>
+      <c r="L37" t="n">
         <v>49</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
-        <v>0.4337</v>
+        <v>0.6133</v>
       </c>
       <c r="N37" t="n">
-        <v>49</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4172</v>
+        <v>0.5871</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2476</v>
+        <v>0.3484</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2528</v>
+        <v>-0.21</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4172</v>
+        <v>0.5871</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6973</v>
+        <v>0.5871</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2801</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6973</v>
+        <v>0.5871</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6973</v>
+        <v>0.5871</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2801</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="L38" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4172</v>
+        <v>0.5871</v>
       </c>
       <c r="N38" t="n">
-        <v>174</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.366</v>
+        <v>0.5333</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2172</v>
+        <v>0.3164</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2735</v>
+        <v>-0.2314</v>
       </c>
       <c r="E39" t="n">
-        <v>0.366</v>
+        <v>0.5333</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.0562</v>
+        <v>0.5333</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4222</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.0562</v>
+        <v>0.5333</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0562</v>
+        <v>0.5333</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4222</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="L39" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.366</v>
+        <v>0.5333</v>
       </c>
       <c r="N39" t="n">
-        <v>242</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3596</v>
+        <v>0.482</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2134</v>
+        <v>0.286</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2761</v>
+        <v>-0.2519</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3596</v>
+        <v>0.482</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9627</v>
+        <v>0.482</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6031</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9627</v>
+        <v>0.482</v>
       </c>
       <c r="I40" t="n">
-        <v>1.9627</v>
+        <v>0.482</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6031</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L40" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3595999999999999</v>
+        <v>0.482</v>
       </c>
       <c r="N40" t="n">
-        <v>258</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3301</v>
+        <v>0.4484</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1959</v>
+        <v>0.2661</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.288</v>
+        <v>-0.2653</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3301</v>
+        <v>0.4484</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3276</v>
+        <v>0.4484</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.3276</v>
+        <v>0.4484</v>
       </c>
       <c r="I41" t="n">
-        <v>1.3276</v>
+        <v>0.4484</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="L41" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3300999999999998</v>
+        <v>0.4484</v>
       </c>
       <c r="N41" t="n">
-        <v>174</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2996</v>
+        <v>0.4443</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1778</v>
+        <v>0.2636</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3003</v>
+        <v>-0.2669</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2996</v>
+        <v>0.4443</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2996</v>
+        <v>1.045</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.6007</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2996</v>
+        <v>1.045</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2996</v>
+        <v>1.045</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.6007</v>
       </c>
       <c r="K42" t="n">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2996</v>
+        <v>0.4442999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>65</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2146</v>
+        <v>0.4337</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1273</v>
+        <v>0.2573</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3347</v>
+        <v>-0.2711</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2146</v>
+        <v>0.4337</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2146</v>
+        <v>0.4337</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2146</v>
+        <v>0.4337</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2146</v>
+        <v>0.4337</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2146</v>
+        <v>0.4337</v>
       </c>
       <c r="N43" t="n">
-        <v>101</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0998</v>
+        <v>0.4225</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0592</v>
+        <v>0.2507</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.381</v>
+        <v>-0.2756</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0998</v>
+        <v>0.4225</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0998</v>
+        <v>2.0256</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-1.6031</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0998</v>
+        <v>2.0256</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0998</v>
+        <v>2.0256</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-1.6031</v>
       </c>
       <c r="K44" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0998</v>
+        <v>0.4224999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>97</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0385</v>
+        <v>0.2996</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0228</v>
+        <v>0.1778</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4058</v>
+        <v>-0.3245</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0385</v>
+        <v>0.2996</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0385</v>
+        <v>0.2996</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0385</v>
+        <v>0.2996</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0385</v>
+        <v>0.2996</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0385</v>
+        <v>0.2996</v>
       </c>
       <c r="N45" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0172</v>
+        <v>0.2902</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0102</v>
+        <v>0.1722</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4144</v>
+        <v>-0.3283</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0172</v>
+        <v>0.2902</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6179</v>
+        <v>0.2902</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.6007</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6179</v>
+        <v>0.2902</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6179</v>
+        <v>0.2902</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.6007</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="L46" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.01719999999999999</v>
+        <v>0.2902</v>
       </c>
       <c r="N46" t="n">
-        <v>174</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.002</v>
+        <v>0.2331</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0012</v>
+        <v>0.1383</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4206</v>
+        <v>-0.351</v>
       </c>
       <c r="E47" t="n">
-        <v>0.002</v>
+        <v>0.2331</v>
       </c>
       <c r="F47" t="n">
-        <v>0.002</v>
+        <v>0.2331</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.002</v>
+        <v>0.2331</v>
       </c>
       <c r="I47" t="n">
-        <v>0.002</v>
+        <v>0.2331</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.002</v>
+        <v>0.2331</v>
       </c>
       <c r="N47" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0337</v>
+        <v>0.233</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.02</v>
+        <v>0.1383</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.435</v>
+        <v>-0.3511</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0337</v>
+        <v>0.233</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0337</v>
+        <v>0.233</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0337</v>
+        <v>0.233</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0337</v>
+        <v>0.233</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0337</v>
+        <v>0.233</v>
       </c>
       <c r="N48" t="n">
         <v>101</v>
@@ -2654,124 +2654,124 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0402</v>
+        <v>0.2039</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0239</v>
+        <v>0.121</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4376</v>
+        <v>-0.3627</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0402</v>
+        <v>0.2039</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.0402</v>
+        <v>0.2039</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.0402</v>
+        <v>0.2039</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0402</v>
+        <v>0.2039</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0402</v>
+        <v>0.2039</v>
       </c>
       <c r="N49" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0803</v>
+        <v>0.1078</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0476</v>
+        <v>0.064</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4538</v>
+        <v>-0.401</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0803</v>
+        <v>0.1078</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0803</v>
+        <v>0.7907</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0803</v>
+        <v>0.7907</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0803</v>
+        <v>0.7907</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="K50" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0803</v>
+        <v>0.1078</v>
       </c>
       <c r="N50" t="n">
-        <v>89</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0891</v>
+        <v>0.0385</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0529</v>
+        <v>0.0228</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4574</v>
+        <v>-0.4286</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0891</v>
+        <v>0.0385</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0891</v>
+        <v>0.0385</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0891</v>
+        <v>0.0385</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0891</v>
+        <v>0.0385</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0891</v>
+        <v>0.0385</v>
       </c>
       <c r="N51" t="n">
         <v>97</v>
@@ -2792,308 +2792,308 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hAdji</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1409</v>
+        <v>-0.01</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0059</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4783</v>
+        <v>-0.4479</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1409</v>
+        <v>-0.01</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1409</v>
+        <v>-0.01</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1409</v>
+        <v>-0.01</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1409</v>
+        <v>-0.01</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1409</v>
+        <v>-0.01</v>
       </c>
       <c r="N52" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1614</v>
+        <v>-0.0337</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0958</v>
+        <v>-0.02</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4866</v>
+        <v>-0.4573</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1614</v>
+        <v>-0.0337</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1614</v>
+        <v>-0.0337</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1614</v>
+        <v>-0.0337</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1614</v>
+        <v>-0.0337</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1614</v>
+        <v>-0.0337</v>
       </c>
       <c r="N53" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>hAdji</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1623</v>
+        <v>-0.1409</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0963</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4869</v>
+        <v>-0.5</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1623</v>
+        <v>-0.1409</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3943</v>
+        <v>-0.1409</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.5566</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3943</v>
+        <v>-0.1409</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3943</v>
+        <v>-0.1409</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.5566</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="L54" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1623</v>
+        <v>-0.1409</v>
       </c>
       <c r="N54" t="n">
-        <v>164</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.182</v>
+        <v>-0.1614</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.108</v>
+        <v>-0.0958</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4949</v>
+        <v>-0.5082</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.182</v>
+        <v>-0.1614</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.182</v>
+        <v>-0.1614</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.182</v>
+        <v>-0.1614</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.182</v>
+        <v>-0.1614</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.182</v>
+        <v>-0.1614</v>
       </c>
       <c r="N55" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1865</v>
+        <v>-0.1623</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1107</v>
+        <v>-0.0963</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4967</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1865</v>
+        <v>-0.1623</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1865</v>
+        <v>0.3943</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-0.5566</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.1865</v>
+        <v>0.3943</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1865</v>
+        <v>0.3943</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-0.5566</v>
       </c>
       <c r="K56" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.1865</v>
+        <v>-0.1623</v>
       </c>
       <c r="N56" t="n">
-        <v>97</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2559</v>
+        <v>-0.182</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1518</v>
+        <v>-0.108</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5164</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2559</v>
+        <v>-0.182</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2559</v>
+        <v>-0.182</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2559</v>
+        <v>-0.182</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2559</v>
+        <v>-0.182</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2559</v>
+        <v>-0.182</v>
       </c>
       <c r="N57" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2704</v>
+        <v>-0.2559</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1605</v>
+        <v>-0.1518</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5306</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2704</v>
+        <v>-0.2559</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2704</v>
+        <v>-0.2559</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2704</v>
+        <v>-0.2559</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2704</v>
+        <v>-0.2559</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2704</v>
+        <v>-0.2559</v>
       </c>
       <c r="N58" t="n">
         <v>65</v>
@@ -3114,139 +3114,139 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2824</v>
+        <v>-0.2704</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1676</v>
+        <v>-0.1605</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5354</v>
+        <v>-0.5516</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2824</v>
+        <v>-0.2704</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2824</v>
+        <v>-0.2704</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2824</v>
+        <v>-0.2704</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2824</v>
+        <v>-0.2704</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2824</v>
+        <v>-0.2704</v>
       </c>
       <c r="N59" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LETN1</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.302</v>
+        <v>-0.2824</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1792</v>
+        <v>-0.1676</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5434</v>
+        <v>-0.5564</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.302</v>
+        <v>-0.2824</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.302</v>
+        <v>-0.2824</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.302</v>
+        <v>-0.2824</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.302</v>
+        <v>-0.2824</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.302</v>
+        <v>-0.2824</v>
       </c>
       <c r="N60" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>LETN1</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3176</v>
+        <v>-0.302</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1885</v>
+        <v>-0.1792</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5497</v>
+        <v>-0.5642</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3176</v>
+        <v>-0.302</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3653</v>
+        <v>-0.302</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.6829</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3653</v>
+        <v>-0.302</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3653</v>
+        <v>-0.302</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.6829</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="L61" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3175999999999999</v>
+        <v>-0.302</v>
       </c>
       <c r="N61" t="n">
-        <v>182</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62">
@@ -3262,7 +3262,7 @@
         <v>-0.1965</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5551</v>
+        <v>-0.5758</v>
       </c>
       <c r="E62" t="n">
         <v>-0.3311</v>
@@ -3308,7 +3308,7 @@
         <v>-0.217</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.5896</v>
       </c>
       <c r="E63" t="n">
         <v>-0.3657</v>
@@ -3344,185 +3344,185 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.5843</v>
+        <v>-0.552</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3467</v>
+        <v>-0.3275</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6574</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5843</v>
+        <v>-0.552</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.5843</v>
+        <v>-0.552</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5843</v>
+        <v>-0.552</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5843</v>
+        <v>-0.552</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.5843</v>
+        <v>-0.552</v>
       </c>
       <c r="N64" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.5843</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3861</v>
+        <v>-0.3467</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6842</v>
+        <v>-0.6767</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.5843</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.9255</v>
+        <v>-0.5843</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2748</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.9255</v>
+        <v>-0.5843</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.9298</v>
+        <v>-0.5843</v>
       </c>
       <c r="J65" t="n">
-        <v>0.2748</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="L65" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.655</v>
+        <v>-0.5843</v>
       </c>
       <c r="N65" t="n">
-        <v>277</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6701</v>
+        <v>-0.6472</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3976</v>
+        <v>-0.384</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6921</v>
+        <v>-0.7018</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6701</v>
+        <v>-0.6472</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6701</v>
+        <v>-0.922</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.2748</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6701</v>
+        <v>-0.922</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6701</v>
+        <v>-0.9298</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>0.2748</v>
       </c>
       <c r="K66" t="n">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6701</v>
+        <v>-0.655</v>
       </c>
       <c r="N66" t="n">
-        <v>48</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7044</v>
+        <v>-0.6701</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.418</v>
+        <v>-0.3976</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7059</v>
+        <v>-0.7109</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7044</v>
+        <v>-0.6701</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7044</v>
+        <v>-0.6701</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7044</v>
+        <v>-0.6701</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7044</v>
+        <v>-0.6701</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7044</v>
+        <v>-0.6701</v>
       </c>
       <c r="N67" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68">
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5171</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7734</v>
+        <v>-0.7894</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="N68" t="n">
         <v>89</v>
@@ -3574,216 +3574,216 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8804</v>
+        <v>-0.8774</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5224</v>
+        <v>-0.5206</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.777</v>
+        <v>-0.7935</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8804</v>
+        <v>-0.8774</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8804</v>
+        <v>-0.8774</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8804</v>
+        <v>-0.8774</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8804</v>
+        <v>-0.8774</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>65</v>
+        <v>173</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8804</v>
+        <v>-0.8774</v>
       </c>
       <c r="N69" t="n">
-        <v>65</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9187</v>
+        <v>-0.8804</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5451</v>
+        <v>-0.5224</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7925</v>
+        <v>-0.7947</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9187</v>
+        <v>-0.8804</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9187</v>
+        <v>-0.8804</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.9187</v>
+        <v>-0.8804</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.9187</v>
+        <v>-0.8804</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.9187</v>
+        <v>-0.8804</v>
       </c>
       <c r="N70" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9757</v>
+        <v>-0.9187</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.579</v>
+        <v>-0.5451</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8155</v>
+        <v>-0.8099</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9757</v>
+        <v>-0.9187</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9757</v>
+        <v>-0.9187</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9757</v>
+        <v>-0.9187</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9757</v>
+        <v>-0.9187</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9757</v>
+        <v>-0.9187</v>
       </c>
       <c r="N71" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NENO</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.985</v>
+        <v>-0.9757</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5845</v>
+        <v>-0.579</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8193</v>
+        <v>-0.8326</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.985</v>
+        <v>-0.9757</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.985</v>
+        <v>-0.9757</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.985</v>
+        <v>-0.9757</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.985</v>
+        <v>-0.9757</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.985</v>
+        <v>-0.9757</v>
       </c>
       <c r="N72" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Impulse</t>
+          <t>NENO</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0087</v>
+        <v>-0.985</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5985</v>
+        <v>-0.5845</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8289</v>
+        <v>-0.8363</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0087</v>
+        <v>-0.985</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0087</v>
+        <v>-0.985</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0087</v>
+        <v>-0.985</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.0087</v>
+        <v>-0.985</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0087</v>
+        <v>-0.985</v>
       </c>
       <c r="N73" t="n">
         <v>49</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Impulse</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0803</v>
+        <v>-1.0087</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.641</v>
+        <v>-0.5985</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8578</v>
+        <v>-0.8458</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0803</v>
+        <v>-1.0087</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.0803</v>
+        <v>-1.0087</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.0803</v>
+        <v>-1.0087</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.0803</v>
+        <v>-1.0087</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.0803</v>
+        <v>-1.0087</v>
       </c>
       <c r="N74" t="n">
-        <v>173</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75">
@@ -3860,7 +3860,7 @@
         <v>-0.6876</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8895</v>
+        <v>-0.9056</v>
       </c>
       <c r="E75" t="n">
         <v>-1.1588</v>
@@ -3906,7 +3906,7 @@
         <v>-0.8806</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0209</v>
+        <v>-1.0352</v>
       </c>
       <c r="E76" t="n">
         <v>-1.4841</v>
@@ -3952,7 +3952,7 @@
         <v>-0.9774</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0868</v>
+        <v>-1.1001</v>
       </c>
       <c r="E77" t="n">
         <v>-1.6471</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1703</v>
+        <v>-1.1825</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8538</v>
@@ -4044,7 +4044,7 @@
         <v>-1.3733</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3563</v>
+        <v>-1.3659</v>
       </c>
       <c r="E79" t="n">
         <v>-2.3143</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.6309</v>
+        <v>-2.6248</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.5611</v>
+        <v>-1.5575</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4842</v>
+        <v>-1.4896</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.6309</v>
+        <v>-2.6248</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.6309</v>
+        <v>-1.6248</v>
       </c>
       <c r="G80" t="n">
         <v>-1</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.6309</v>
+        <v>-1.6248</v>
       </c>
       <c r="I80" t="n">
         <v>-1.6385</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.6124</v>
+        <v>-3.6047</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.1435</v>
+        <v>-2.139</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8807</v>
+        <v>-1.88</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.6124</v>
+        <v>-3.6047</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.0624</v>
+        <v>-2.0547</v>
       </c>
       <c r="G81" t="n">
         <v>-1.55</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.0624</v>
+        <v>-2.0547</v>
       </c>
       <c r="I81" t="n">
         <v>-2.072</v>
